--- a/tools/importer/reports/import-adventure-detail.report.xlsx
+++ b/tools/importer/reports/import-adventure-detail.report.xlsx
@@ -52,7 +52,7 @@
     <t>adventure-detail</t>
   </si>
   <si>
-    <t>2026-09-09T12:44:44.679Z</t>
+    <t>2026-09-10T04:21:13.060Z</t>
   </si>
   <si>
     <t>Bali Surf Camp</t>
@@ -67,7 +67,7 @@
     <t>ca/en/adventures/beervana-portland</t>
   </si>
   <si>
-    <t>2026-09-09T12:44:48.731Z</t>
+    <t>2026-09-10T04:21:17.908Z</t>
   </si>
   <si>
     <t>Beervana in Portland</t>
@@ -82,7 +82,7 @@
     <t>ca/en/adventures/climbing-new-zealand</t>
   </si>
   <si>
-    <t>2026-09-09T12:44:53.505Z</t>
+    <t>2026-09-10T04:21:22.945Z</t>
   </si>
   <si>
     <t>Climbing New Zealand</t>
@@ -97,7 +97,7 @@
     <t>ca/en/adventures/colorado-rock-climbing</t>
   </si>
   <si>
-    <t>2026-09-09T12:44:58.228Z</t>
+    <t>2026-09-10T04:21:27.788Z</t>
   </si>
   <si>
     <t>Colorado Rock Climbing</t>
@@ -112,7 +112,7 @@
     <t>ca/en/adventures/cycling-southern-utah</t>
   </si>
   <si>
-    <t>2026-09-09T12:45:03.615Z</t>
+    <t>2026-09-10T04:21:33.952Z</t>
   </si>
   <si>
     <t>Cycling Southern Utah</t>
@@ -127,7 +127,7 @@
     <t>ca/en/adventures/cycling-tuscany</t>
   </si>
   <si>
-    <t>2026-09-09T12:45:08.257Z</t>
+    <t>2026-09-10T04:21:38.721Z</t>
   </si>
   <si>
     <t>Cycling Tuscany</t>
@@ -142,7 +142,7 @@
     <t>ca/en/adventures/downhill-skiing-wyoming</t>
   </si>
   <si>
-    <t>2026-09-09T12:45:13.957Z</t>
+    <t>2026-09-10T04:21:43.907Z</t>
   </si>
   <si>
     <t>Downhill Skiing Wyoming</t>
@@ -157,7 +157,7 @@
     <t>ca/en/adventures/gastronomic-marais-tour</t>
   </si>
   <si>
-    <t>2026-09-09T12:45:19.510Z</t>
+    <t>2026-09-10T04:21:49.036Z</t>
   </si>
   <si>
     <t>Gastronomic Marais Tour</t>
@@ -172,7 +172,7 @@
     <t>ca/en/adventures/napa-wine-tasting</t>
   </si>
   <si>
-    <t>2026-09-09T12:45:24.215Z</t>
+    <t>2026-09-10T04:21:54.276Z</t>
   </si>
   <si>
     <t>Napa Wine Tasting</t>
@@ -187,7 +187,7 @@
     <t>ca/en/adventures/riverside-camping-australia</t>
   </si>
   <si>
-    <t>2026-09-09T12:45:28.584Z</t>
+    <t>2026-09-10T04:22:01.013Z</t>
   </si>
   <si>
     <t>Riverside Camping</t>
@@ -202,7 +202,7 @@
     <t>ca/en/adventures/ski-touring-mont-blanc</t>
   </si>
   <si>
-    <t>2026-09-09T12:45:33.504Z</t>
+    <t>2026-09-10T04:22:07.159Z</t>
   </si>
   <si>
     <t>Ski Touring Mont Blanc</t>
@@ -217,7 +217,7 @@
     <t>ca/en/adventures/surf-camp-costa-rica</t>
   </si>
   <si>
-    <t>2026-09-09T12:45:38.937Z</t>
+    <t>2026-09-10T04:22:12.150Z</t>
   </si>
   <si>
     <t>Surf Camp in Costa Rica</t>
@@ -232,7 +232,7 @@
     <t>ca/en/adventures/tahoe-skiing</t>
   </si>
   <si>
-    <t>2026-09-09T12:45:43.791Z</t>
+    <t>2026-09-10T04:22:17.798Z</t>
   </si>
   <si>
     <t>Tahoe Skiing</t>
@@ -247,7 +247,7 @@
     <t>ca/en/adventures/west-coast-cycling</t>
   </si>
   <si>
-    <t>2026-09-09T12:45:49.272Z</t>
+    <t>2026-09-10T04:22:22.826Z</t>
   </si>
   <si>
     <t>West Coast Cycling</t>
@@ -262,7 +262,7 @@
     <t>ca/en/adventures/whistler-mountain-biking</t>
   </si>
   <si>
-    <t>2026-09-09T12:45:54.973Z</t>
+    <t>2026-09-10T04:22:27.679Z</t>
   </si>
   <si>
     <t>Whistler Mountain Biking</t>
@@ -277,7 +277,7 @@
     <t>ca/en/adventures/yosemite-backpacking</t>
   </si>
   <si>
-    <t>2026-09-09T12:46:00.329Z</t>
+    <t>2026-09-10T04:22:31.663Z</t>
   </si>
   <si>
     <t>Yosemite Backpacking</t>
@@ -292,7 +292,7 @@
     <t>us/en/adventures/bali-surf-camp</t>
   </si>
   <si>
-    <t>2026-09-09T12:46:06.613Z</t>
+    <t>2026-09-10T04:22:37.429Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/bali-surf-camp.html</t>
@@ -304,7 +304,7 @@
     <t>us/en/adventures/beervana-portland</t>
   </si>
   <si>
-    <t>2026-09-09T12:46:12.533Z</t>
+    <t>2026-09-10T04:22:43.038Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/beervana-portland.html</t>
@@ -316,7 +316,7 @@
     <t>us/en/adventures/climbing-new-zealand</t>
   </si>
   <si>
-    <t>2026-09-09T12:46:16.450Z</t>
+    <t>2026-09-10T04:22:48.081Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/climbing-new-zealand.html</t>
@@ -328,7 +328,7 @@
     <t>us/en/adventures/colorado-rock-climbing</t>
   </si>
   <si>
-    <t>2026-09-09T12:46:20.764Z</t>
+    <t>2026-09-10T04:22:52.855Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/colorado-rock-climbing.html</t>
@@ -340,7 +340,7 @@
     <t>us/en/adventures/cycling-southern-utah</t>
   </si>
   <si>
-    <t>2026-09-09T12:46:26.518Z</t>
+    <t>2026-09-10T04:22:59.397Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/cycling-southern-utah.html</t>
@@ -352,7 +352,7 @@
     <t>us/en/adventures/cycling-tuscany</t>
   </si>
   <si>
-    <t>2026-09-09T12:46:32.354Z</t>
+    <t>2026-09-10T04:23:05.509Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/cycling-tuscany.html</t>
@@ -364,7 +364,7 @@
     <t>us/en/adventures/downhill-skiing-wyoming</t>
   </si>
   <si>
-    <t>2026-09-09T12:46:36.864Z</t>
+    <t>2026-09-10T04:23:11.185Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/downhill-skiing-wyoming.html</t>
@@ -376,7 +376,7 @@
     <t>us/en/adventures/gastronomic-marais-tour</t>
   </si>
   <si>
-    <t>2026-09-09T12:46:42.276Z</t>
+    <t>2026-09-10T04:23:17.516Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/gastronomic-marais-tour.html</t>
@@ -388,7 +388,7 @@
     <t>us/en/adventures/napa-wine-tasting</t>
   </si>
   <si>
-    <t>2026-09-09T12:46:48.103Z</t>
+    <t>2026-09-10T04:23:22.732Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/napa-wine-tasting.html</t>
@@ -400,7 +400,7 @@
     <t>us/en/adventures/riverside-camping-australia</t>
   </si>
   <si>
-    <t>2026-09-09T12:46:52.505Z</t>
+    <t>2026-09-10T04:23:28.315Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/riverside-camping-australia.html</t>
@@ -412,7 +412,7 @@
     <t>us/en/adventures/ski-touring-mont-blanc</t>
   </si>
   <si>
-    <t>2026-09-09T12:46:57.474Z</t>
+    <t>2026-09-10T04:23:36.609Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/ski-touring-mont-blanc.html</t>
@@ -424,7 +424,7 @@
     <t>us/en/adventures/surf-camp-costa-rica</t>
   </si>
   <si>
-    <t>2026-09-09T12:47:01.655Z</t>
+    <t>2026-09-10T04:23:44.395Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/surf-camp-costa-rica.html</t>
@@ -436,7 +436,7 @@
     <t>us/en/adventures/tahoe-skiing</t>
   </si>
   <si>
-    <t>2026-09-09T12:47:06.307Z</t>
+    <t>2026-09-10T04:23:49.687Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/tahoe-skiing.html</t>
@@ -448,7 +448,7 @@
     <t>us/en/adventures/west-coast-cycling</t>
   </si>
   <si>
-    <t>2026-09-09T12:47:11.591Z</t>
+    <t>2026-09-10T04:23:54.529Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/west-coast-cycling.html</t>
@@ -460,7 +460,7 @@
     <t>us/en/adventures/whistler-mountain-biking</t>
   </si>
   <si>
-    <t>2026-09-09T12:47:15.854Z</t>
+    <t>2026-09-10T04:24:01.296Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/whistler-mountain-biking.html</t>
@@ -472,7 +472,7 @@
     <t>us/en/adventures/yosemite-backpacking</t>
   </si>
   <si>
-    <t>2026-09-09T12:47:21.098Z</t>
+    <t>2026-09-10T04:24:08.437Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/yosemite-backpacking.html</t>
